--- a/lecture_slides/08_chapter_hypothesis_tests/data/vungle_one_sample_tests.xlsx
+++ b/lecture_slides/08_chapter_hypothesis_tests/data/vungle_one_sample_tests.xlsx
@@ -10,8 +10,6 @@
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
     <sheet name="One_Sample_t" sheetId="2" r:id="rId2"/>
     <sheet name="One_Proportion_z" sheetId="3" r:id="rId3"/>
-    <sheet name="Heathrow_t" sheetId="4" r:id="rId4"/>
-    <sheet name="PineCreek_z" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2357,188 +2355,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Sample mean</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Sample std dev</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>1.052</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>mu0</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>t Stat</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>1.840771552379951</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P(T&gt;t) one-tail</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0.0353425542208883</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Women</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>p-hat</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>p0</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>z Stat</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P(Z&gt;z) one-tail</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0.006209665325776142</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>